--- a/data/trans_orig/P1418-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2007</t>
+          <t>Población con diagnóstico de mala circulación en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>899</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7584</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>9133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489802</t>
+          <t>489900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>459905</t>
+          <t>459855</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466584</t>
+          <t>466590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>952507</t>
+          <t>952420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960621</t>
+          <t>960616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2559</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14289</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9987</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14300</t>
+          <t>14830</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35706</t>
+          <t>34856</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>721200</t>
+          <t>720707</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732930</t>
+          <t>732903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598093</t>
+          <t>598938</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615507</t>
+          <t>615431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1325276</t>
+          <t>1326126</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1346682</t>
+          <t>1346152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27320</t>
+          <t>26385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>52612</t>
+          <t>50999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36469</t>
+          <t>37160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64443</t>
+          <t>63693</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>618128</t>
+          <t>617275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632067</t>
+          <t>632060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637132</t>
+          <t>638745</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>662424</t>
+          <t>663359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1263969</t>
+          <t>1264719</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291943</t>
+          <t>1291252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17343</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>39065</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37921</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67063</t>
+          <t>65114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61948</t>
+          <t>61098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96666</t>
+          <t>96765</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>479550</t>
+          <t>480082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501804</t>
+          <t>501161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448579</t>
+          <t>450528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>477721</t>
+          <t>476865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>938123</t>
+          <t>938024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>972841</t>
+          <t>973691</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>34092</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58053</t>
+          <t>58633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36475</t>
+          <t>36961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61878</t>
+          <t>63163</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>75825</t>
+          <t>76285</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>111627</t>
+          <t>114265</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328657</t>
+          <t>328077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>354288</t>
+          <t>352618</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>342108</t>
+          <t>340823</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>367511</t>
+          <t>367025</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>679069</t>
+          <t>676431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>714871</t>
+          <t>714411</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,35%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32454</t>
+          <t>32620</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55410</t>
+          <t>56223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>66557</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97607</t>
+          <t>97082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>107009</t>
+          <t>106418</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>145295</t>
+          <t>144351</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237173</t>
+          <t>236360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260129</t>
+          <t>259963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245327</t>
+          <t>245852</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274892</t>
+          <t>276377</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490222</t>
+          <t>491166</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>528508</t>
+          <t>529099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,25%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33908</t>
+          <t>34286</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56159</t>
+          <t>56503</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86512</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122947</t>
+          <t>122887</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128939</t>
+          <t>129895</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>171825</t>
+          <t>172557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153724</t>
+          <t>153380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175975</t>
+          <t>175597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>210961</t>
+          <t>211021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>247396</t>
+          <t>247515</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,09%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>371966</t>
+          <t>371234</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>414852</t>
+          <t>413896</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156679</t>
+          <t>154201</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>208697</t>
+          <t>205646</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>312259</t>
+          <t>308880</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>382390</t>
+          <t>381226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>477027</t>
+          <t>482505</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>568283</t>
+          <t>564282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3067846</t>
+          <t>3070897</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3119864</t>
+          <t>3122342</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2996807</t>
+          <t>2997971</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3066938</t>
+          <t>3070317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6087458</t>
+          <t>6091459</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6178714</t>
+          <t>6173236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2012</t>
+          <t>Población con diagnóstico de mala circulación en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4595</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>978</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4911</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4712</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425319</t>
+          <t>425635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879664</t>
+          <t>879505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>679569</t>
+          <t>680118</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686171</t>
+          <t>686175</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>597798</t>
+          <t>599195</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608237</t>
+          <t>608273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1281028</t>
+          <t>1281788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293437</t>
+          <t>1293293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42527</t>
+          <t>40878</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21695</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46830</t>
+          <t>47342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>669371</t>
+          <t>670127</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680965</t>
+          <t>680962</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>667047</t>
+          <t>668696</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690277</t>
+          <t>690362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1344607</t>
+          <t>1344095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1369742</t>
+          <t>1369305</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4461</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20803</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28271</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53171</t>
+          <t>51034</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>35825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64504</t>
+          <t>65214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>593814</t>
+          <t>594695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>610156</t>
+          <t>609740</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>560046</t>
+          <t>562183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>584946</t>
+          <t>587492</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1163330</t>
+          <t>1162620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1191774</t>
+          <t>1192009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7926</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>22531</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46181</t>
+          <t>45326</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73821</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>57660</t>
+          <t>56535</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91109</t>
+          <t>90199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406085</t>
+          <t>406898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421503</t>
+          <t>421429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>373979</t>
+          <t>372383</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>401619</t>
+          <t>402474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>786120</t>
+          <t>787030</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>819569</t>
+          <t>820694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21650</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59109</t>
+          <t>59381</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89353</t>
+          <t>89888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85112</t>
+          <t>87330</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123296</t>
+          <t>124213</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264233</t>
+          <t>264642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288136</t>
+          <t>288352</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264643</t>
+          <t>264108</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294887</t>
+          <t>294615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>540486</t>
+          <t>539569</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>578670</t>
+          <t>576452</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31862</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57387</t>
+          <t>57146</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>121381</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160583</t>
+          <t>160151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161127</t>
+          <t>160501</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205972</t>
+          <t>209912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192464</t>
+          <t>192705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>217989</t>
+          <t>218342</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228396</t>
+          <t>228828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267598</t>
+          <t>267995</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>432858</t>
+          <t>428918</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477703</t>
+          <t>478329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>88191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>130977</t>
+          <t>128787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>311242</t>
+          <t>309986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>384600</t>
+          <t>383820</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>409172</t>
+          <t>413206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>496939</t>
+          <t>494468</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3295802</t>
+          <t>3297992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3339412</t>
+          <t>3338588</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3169452</t>
+          <t>3170232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3242810</t>
+          <t>3244066</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6483892</t>
+          <t>6486363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6571659</t>
+          <t>6567625</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2016</t>
+          <t>Población con diagnóstico de mala circulación en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,62 +6726,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5226</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6287</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413914</t>
+          <t>413865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>808931</t>
+          <t>809992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2936</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14567</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15623</t>
+          <t>16601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585719</t>
+          <t>585766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>548977</t>
+          <t>549385</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560608</t>
+          <t>560572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1138417</t>
+          <t>1137439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150244</t>
+          <t>1150141</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26053</t>
+          <t>27481</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26774</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>667086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>669097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635333</t>
+          <t>633905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651137</t>
+          <t>651245</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1303709</t>
+          <t>1304111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319427</t>
+          <t>1319657</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5582</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>20037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>48742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>624362</t>
+          <t>626011</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640305</t>
+          <t>640466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>610008</t>
+          <t>612401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633088</t>
+          <t>633108</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1244312</t>
+          <t>1246383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1269282</t>
+          <t>1270436</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>23639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35978</t>
+          <t>34202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65021</t>
+          <t>62328</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47428</t>
+          <t>47780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79341</t>
+          <t>81277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454385</t>
+          <t>454279</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470510</t>
+          <t>470402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>431828</t>
+          <t>434521</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>460871</t>
+          <t>462647</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>895426</t>
+          <t>893490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>927339</t>
+          <t>926987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13439</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31846</t>
+          <t>30838</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46985</t>
+          <t>46795</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>75989</t>
+          <t>76862</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65608</t>
+          <t>65773</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>98237</t>
+          <t>101906</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>302484</t>
+          <t>303492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>320891</t>
+          <t>321628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>301773</t>
+          <t>300900</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330777</t>
+          <t>330967</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>613855</t>
+          <t>610186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646484</t>
+          <t>646319</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,76%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23942</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44205</t>
+          <t>46429</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77617</t>
+          <t>76812</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114568</t>
+          <t>114605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>109966</t>
+          <t>103866</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>152025</t>
+          <t>149801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,8%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>212793</t>
+          <t>210569</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233056</t>
+          <t>232141</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285601</t>
+          <t>285564</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>322552</t>
+          <t>323357</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>505142</t>
+          <t>507366</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>547201</t>
+          <t>553301</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>84,19%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65743</t>
+          <t>64345</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>104793</t>
+          <t>99877</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>222347</t>
+          <t>223146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>286891</t>
+          <t>289290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>298226</t>
+          <t>301375</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>372207</t>
+          <t>373029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3289557</t>
+          <t>3294473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3328607</t>
+          <t>3330005</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3257651</t>
+          <t>3255252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3322195</t>
+          <t>3321396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6566685</t>
+          <t>6565863</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6640666</t>
+          <t>6637517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de mala circulación en 2023</t>
+          <t>Población con diagnóstico de mala circulación en 2023 (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20294</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14799</t>
+          <t>19772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1551</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>24132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379693</t>
+          <t>376840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298401</t>
+          <t>293428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>688409</t>
+          <t>689055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711636</t>
+          <t>711591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1835</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11299</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418011</t>
+          <t>417748</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500044</t>
+          <t>499012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509508</t>
+          <t>509547</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922231</t>
+          <t>921497</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932720</t>
+          <t>932463</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12312</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>11371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25859</t>
+          <t>25551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16288</t>
+          <t>16020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521561</t>
+          <t>521242</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531873</t>
+          <t>531849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>515774</t>
+          <t>516082</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>529490</t>
+          <t>530262</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1042423</t>
+          <t>1042629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059218</t>
+          <t>1059486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10812</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>43401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44117</t>
+          <t>44857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74527</t>
+          <t>76946</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52773</t>
+          <t>52808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>107068</t>
+          <t>108614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843834</t>
+          <t>843329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875918</t>
+          <t>875603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>635153</t>
+          <t>632734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>665563</t>
+          <t>664823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1489342</t>
+          <t>1487796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1543637</t>
+          <t>1543602</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,7 +10897,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40397</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45460</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66672</t>
+          <t>67277</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70893</t>
+          <t>69818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98799</t>
+          <t>98769</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,94%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>519840</t>
+          <t>520613</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>539488</t>
+          <t>540089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>477425</t>
+          <t>476820</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498637</t>
+          <t>498940</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1005534</t>
+          <t>1005564</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1033440</t>
+          <t>1034515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23209</t>
+          <t>22688</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40360</t>
+          <t>39764</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19739</t>
+          <t>19426</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81132</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40887</t>
+          <t>43555</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>110002</t>
+          <t>108847</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327087</t>
+          <t>327683</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344238</t>
+          <t>344759</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>526357</t>
+          <t>526868</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>587750</t>
+          <t>588063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>864934</t>
+          <t>866089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>934049</t>
+          <t>931381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>34869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53051</t>
+          <t>53030</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98266</t>
+          <t>99028</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>124167</t>
+          <t>123511</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>139182</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>173099</t>
+          <t>172689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229708</t>
+          <t>229729</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>248540</t>
+          <t>247890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301051</t>
+          <t>301707</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326952</t>
+          <t>326190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>534878</t>
+          <t>535288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>568795</t>
+          <t>567188</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>109528</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162460</t>
+          <t>163291</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>246863</t>
+          <t>251747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>339833</t>
+          <t>340066</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>379743</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>493400</t>
+          <t>483252</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3292120</t>
+          <t>3291289</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3345875</t>
+          <t>3345052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3312826</t>
+          <t>3312593</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3405796</t>
+          <t>3400912</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6613839</t>
+          <t>6623987</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6719803</t>
+          <t>6727496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1418-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1418-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4164</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>898</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9133</t>
+          <t>8794</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489900</t>
+          <t>489941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>459855</t>
+          <t>459937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>466590</t>
+          <t>466591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>952420</t>
+          <t>952759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>960616</t>
+          <t>960615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26556</t>
+          <t>27016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14830</t>
+          <t>14291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34856</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>720707</t>
+          <t>722776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>732903</t>
+          <t>732962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>598938</t>
+          <t>598478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>615431</t>
+          <t>615638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1326126</t>
+          <t>1325931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1346152</t>
+          <t>1346691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6710</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>21702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26385</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50999</t>
+          <t>50470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37160</t>
+          <t>36814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63693</t>
+          <t>64871</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>617275</t>
+          <t>616966</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632060</t>
+          <t>631958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>638745</t>
+          <t>639274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>663359</t>
+          <t>662305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1264719</t>
+          <t>1263541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1291252</t>
+          <t>1291598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>17682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>40470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65114</t>
+          <t>66864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61098</t>
+          <t>60504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96765</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>480082</t>
+          <t>478677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>501161</t>
+          <t>501465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>450528</t>
+          <t>448778</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>476865</t>
+          <t>476762</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>938024</t>
+          <t>940492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>973691</t>
+          <t>974285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34092</t>
+          <t>33364</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58633</t>
+          <t>58304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36961</t>
+          <t>35777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63163</t>
+          <t>61758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>76285</t>
+          <t>76681</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114265</t>
+          <t>111950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>328077</t>
+          <t>328406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>352618</t>
+          <t>353346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>340823</t>
+          <t>342228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>367025</t>
+          <t>368209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>676431</t>
+          <t>678746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>714411</t>
+          <t>714015</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32620</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56223</t>
+          <t>56208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>66557</t>
+          <t>66931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97082</t>
+          <t>96488</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>106418</t>
+          <t>104919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>144351</t>
+          <t>143206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236360</t>
+          <t>236375</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259963</t>
+          <t>259541</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>245852</t>
+          <t>246446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276377</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>491166</t>
+          <t>492311</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>529099</t>
+          <t>530598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,49%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>35215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56503</t>
+          <t>57967</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>86911</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122887</t>
+          <t>122354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>130908</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172557</t>
+          <t>172679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>153380</t>
+          <t>151916</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>175597</t>
+          <t>174668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>211021</t>
+          <t>211554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>247515</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>371234</t>
+          <t>371112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413896</t>
+          <t>412883</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>154201</t>
+          <t>156040</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>205646</t>
+          <t>206738</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>308880</t>
+          <t>309379</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>381226</t>
+          <t>378888</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>482505</t>
+          <t>475182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>564282</t>
+          <t>565293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3070897</t>
+          <t>3069805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3122342</t>
+          <t>3120503</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2997971</t>
+          <t>3000309</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3070317</t>
+          <t>3069818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6091459</t>
+          <t>6090448</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6173236</t>
+          <t>6180559</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,86%</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425635</t>
+          <t>426284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>879505</t>
+          <t>879459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>913</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11060</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>17055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>680118</t>
+          <t>679557</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>686175</t>
+          <t>686174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>599195</t>
+          <t>598628</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>608273</t>
+          <t>608223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1281788</t>
+          <t>1280287</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1293293</t>
+          <t>1292617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11736</t>
+          <t>12763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19212</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22132</t>
+          <t>21974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>47329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>670127</t>
+          <t>669100</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680962</t>
+          <t>680967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>668696</t>
+          <t>666663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>690362</t>
+          <t>689881</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1344095</t>
+          <t>1344108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1369305</t>
+          <t>1369463</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>25817</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51034</t>
+          <t>49796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35825</t>
+          <t>36239</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65214</t>
+          <t>65925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>594695</t>
+          <t>595269</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>609740</t>
+          <t>609424</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>562183</t>
+          <t>563421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>587492</t>
+          <t>587400</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1162620</t>
+          <t>1161909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192009</t>
+          <t>1191595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,05%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22531</t>
+          <t>22623</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45326</t>
+          <t>44996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75417</t>
+          <t>73936</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56535</t>
+          <t>58192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>90199</t>
+          <t>90825</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>406898</t>
+          <t>406806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>421429</t>
+          <t>421328</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>372383</t>
+          <t>373864</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>402474</t>
+          <t>402804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>787030</t>
+          <t>786404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>820694</t>
+          <t>819037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,37%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45144</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>59158</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>89888</t>
+          <t>88803</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>87330</t>
+          <t>87206</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>124213</t>
+          <t>125861</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264642</t>
+          <t>265892</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>288352</t>
+          <t>287909</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>264108</t>
+          <t>265193</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>294615</t>
+          <t>294838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539569</t>
+          <t>537921</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>576452</t>
+          <t>576576</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57146</t>
+          <t>58086</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120984</t>
+          <t>121479</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160151</t>
+          <t>158914</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>160501</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209912</t>
+          <t>204754</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>192705</t>
+          <t>191765</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218342</t>
+          <t>217942</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>228828</t>
+          <t>230065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>267995</t>
+          <t>267500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>428918</t>
+          <t>434076</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>478329</t>
+          <t>479139</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>75,0%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88191</t>
+          <t>86064</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128787</t>
+          <t>129575</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>309986</t>
+          <t>312931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>383820</t>
+          <t>383193</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>413206</t>
+          <t>412841</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>494468</t>
+          <t>497025</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3297992</t>
+          <t>3297204</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3338588</t>
+          <t>3340715</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3170232</t>
+          <t>3170859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3244066</t>
+          <t>3241121</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6486363</t>
+          <t>6483806</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6567625</t>
+          <t>6567990</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5226</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>413865</t>
+          <t>413889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>809992</t>
+          <t>808885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3882</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585766</t>
+          <t>584742</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>549385</t>
+          <t>548866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>560572</t>
+          <t>560328</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1137439</t>
+          <t>1137417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1150141</t>
+          <t>1150158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27481</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10826</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26372</t>
+          <t>26662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>633905</t>
+          <t>634744</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651245</t>
+          <t>651190</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1304111</t>
+          <t>1303821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1319657</t>
+          <t>1320483</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5582</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>20163</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15969</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36676</t>
+          <t>36455</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24689</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48742</t>
+          <t>49679</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>626011</t>
+          <t>625885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>640466</t>
+          <t>640311</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>612401</t>
+          <t>612622</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>633108</t>
+          <t>633230</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1246383</t>
+          <t>1245446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1270436</t>
+          <t>1270167</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23639</t>
+          <t>23824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8083,7 +8083,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34202</t>
+          <t>35785</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>62328</t>
+          <t>64653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47780</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81277</t>
+          <t>81324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>454279</t>
+          <t>454094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470402</t>
+          <t>470415</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>434521</t>
+          <t>432196</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>462647</t>
+          <t>461064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>893490</t>
+          <t>893443</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>926987</t>
+          <t>926344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>12908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30838</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46795</t>
+          <t>46639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>76862</t>
+          <t>76173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65773</t>
+          <t>64543</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101906</t>
+          <t>99966</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>303492</t>
+          <t>303361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>321628</t>
+          <t>321422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>300900</t>
+          <t>301589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330967</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>610186</t>
+          <t>612126</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>646319</t>
+          <t>647549</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,94%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24857</t>
+          <t>23873</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>44345</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>76812</t>
+          <t>77998</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>114605</t>
+          <t>114419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>103866</t>
+          <t>106805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149801</t>
+          <t>149920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,81%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210569</t>
+          <t>212653</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>232141</t>
+          <t>233125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>285564</t>
+          <t>285750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>323357</t>
+          <t>322171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>507366</t>
+          <t>507247</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>553301</t>
+          <t>550362</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64345</t>
+          <t>64449</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99877</t>
+          <t>101690</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>223146</t>
+          <t>222423</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>289290</t>
+          <t>285859</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>301375</t>
+          <t>294386</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>373029</t>
+          <t>373711</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3294473</t>
+          <t>3292660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3330005</t>
+          <t>3329901</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3255252</t>
+          <t>3258683</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3321396</t>
+          <t>3322119</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6565863</t>
+          <t>6565181</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6637517</t>
+          <t>6644506</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9675,12 +9675,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4309</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19772</t>
+          <t>17361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -9725,7 +9725,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1596</t>
+          <t>2038</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -9778,27 +9778,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>396164</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376840</t>
+          <t>386926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -9813,27 +9813,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>308891</t>
+          <t>358108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>293428</t>
+          <t>345151</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>705055</t>
+          <t>762511</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>689055</t>
+          <t>749053</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>711591</t>
+          <t>768267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1202</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -10018,12 +10018,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5799</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -10033,7 +10033,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>5063</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1796</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>11702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13393</t>
+          <t>12920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -10121,27 +10121,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422418</t>
+          <t>475688</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417748</t>
+          <t>469669</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>506230</t>
+          <t>495103</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>499012</t>
+          <t>488464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>509547</t>
+          <t>498229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>928648</t>
+          <t>970791</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>921497</t>
+          <t>964136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932463</t>
+          <t>974739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511343</t>
+          <t>500166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934890</t>
+          <t>977056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,67 +10351,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5455</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12631</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>21760</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>14687</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30412</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>2,37%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17845</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11371</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25551</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23301</t>
+          <t>27691</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16020</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -10464,69 +10464,69 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>528418</t>
+          <t>612374</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>521242</t>
+          <t>604694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>531849</t>
+          <t>616052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>599174</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>590522</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>606247</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>97,63%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>523788</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>516082</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>530262</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1354</t>
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1052205</t>
+          <t>1211548</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1042629</t>
+          <t>1201042</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1059486</t>
+          <t>1219732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533873</t>
+          <t>618305</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533873</t>
+          <t>618305</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533873</t>
+          <t>618305</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541633</t>
+          <t>620934</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541633</t>
+          <t>620934</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541633</t>
+          <t>620934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075506</t>
+          <t>1239239</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075506</t>
+          <t>1239239</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075506</t>
+          <t>1239239</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>19201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43401</t>
+          <t>41498</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>57123</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44857</t>
+          <t>45794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>76946</t>
+          <t>68789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>85756</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52808</t>
+          <t>71001</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108614</t>
+          <t>102757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>860705</t>
+          <t>670890</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>843329</t>
+          <t>658024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>875603</t>
+          <t>680321</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>652783</t>
+          <t>676501</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>632734</t>
+          <t>664835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>664823</t>
+          <t>687830</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1513488</t>
+          <t>1347390</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1487796</t>
+          <t>1330389</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1543602</t>
+          <t>1362145</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886730</t>
+          <t>699522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>709680</t>
+          <t>733624</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>709680</t>
+          <t>733624</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>709680</t>
+          <t>733624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1596410</t>
+          <t>1433146</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1596410</t>
+          <t>1433146</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1596410</t>
+          <t>1433146</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>29881</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20148</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>41381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,22 +11072,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>60897</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>45157</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>73591</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -11097,7 +11097,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>83873</t>
+          <t>90778</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69818</t>
+          <t>76544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>98769</t>
+          <t>106849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>531610</t>
+          <t>578478</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>520613</t>
+          <t>566978</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>540089</t>
+          <t>587263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,27 +11185,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>488851</t>
+          <t>545161</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>476820</t>
+          <t>532467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498940</t>
+          <t>555739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1020460</t>
+          <t>1123639</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1005564</t>
+          <t>1107568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1034515</t>
+          <t>1137873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30608</t>
+          <t>32221</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22688</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39764</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>51372</t>
+          <t>57198</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19426</t>
+          <t>47555</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80621</t>
+          <t>67710</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>81979</t>
+          <t>89419</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43555</t>
+          <t>75995</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108847</t>
+          <t>104890</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>336839</t>
+          <t>373990</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>327683</t>
+          <t>364027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>344759</t>
+          <t>381967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>556117</t>
+          <t>380995</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>526868</t>
+          <t>370483</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>588063</t>
+          <t>390638</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>892957</t>
+          <t>754985</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>866089</t>
+          <t>739514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>931381</t>
+          <t>768409</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367447</t>
+          <t>406211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607489</t>
+          <t>438193</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607489</t>
+          <t>438193</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607489</t>
+          <t>438193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974936</t>
+          <t>844404</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974936</t>
+          <t>844404</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974936</t>
+          <t>844404</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>43241</t>
+          <t>48308</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53030</t>
+          <t>58647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>111897</t>
+          <t>122479</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>99028</t>
+          <t>109576</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>123511</t>
+          <t>137575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>155139</t>
+          <t>170786</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>140789</t>
+          <t>154332</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172689</t>
+          <t>188230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,31%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>239518</t>
+          <t>261890</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229729</t>
+          <t>251551</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247890</t>
+          <t>272756</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>313321</t>
+          <t>341475</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>301707</t>
+          <t>326379</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>326190</t>
+          <t>354378</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>552838</t>
+          <t>603367</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>535288</t>
+          <t>585923</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>567188</t>
+          <t>619821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425218</t>
+          <t>463954</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425218</t>
+          <t>463954</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425218</t>
+          <t>463954</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707977</t>
+          <t>774153</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707977</t>
+          <t>774153</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707977</t>
+          <t>774153</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>138907</t>
+          <t>149565</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109528</t>
+          <t>127983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>163291</t>
+          <t>172386</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>302680</t>
+          <t>328924</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>251747</t>
+          <t>301096</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>340066</t>
+          <t>357002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>441588</t>
+          <t>478489</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>379743</t>
+          <t>443396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>483252</t>
+          <t>517126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3315673</t>
+          <t>3377714</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3291289</t>
+          <t>3354893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3345052</t>
+          <t>3399296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3349979</t>
+          <t>3396518</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3312593</t>
+          <t>3368440</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3400912</t>
+          <t>3424346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6665651</t>
+          <t>6774232</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6623987</t>
+          <t>6735595</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6727496</t>
+          <t>6809325</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3454580</t>
+          <t>3527279</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3652659</t>
+          <t>3725442</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7107239</t>
+          <t>7252721</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
